--- a/fall-2022/Attendance.xlsx
+++ b/fall-2022/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VIP\Github_repos\vip-nlp\fall-2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E2B00C-D806-40D1-820C-3205CD0A3FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B91CCCD-45E2-40DC-BB55-1A5356A83303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -379,9 +379,7 @@
       <c r="L1" s="2">
         <v>44883</v>
       </c>
-      <c r="M1" s="2">
-        <v>44890</v>
-      </c>
+      <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -404,12 +402,12 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -435,7 +433,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="G3" s="6"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -556,7 +554,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -586,7 +584,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>

--- a/fall-2022/Attendance.xlsx
+++ b/fall-2022/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VIP\Github_repos\vip-nlp\fall-2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B91CCCD-45E2-40DC-BB55-1A5356A83303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC67EF81-7887-4F83-B9F6-27D4C7452F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -437,7 +437,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="K3" s="6"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -587,7 +587,7 @@
       <c r="H8" s="6"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
